--- a/docs/cadrage/artefacts/equipe-11-release-planning-v2.1.xlsx
+++ b/docs/cadrage/artefacts/equipe-11-release-planning-v2.1.xlsx
@@ -750,7 +750,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -877,7 +877,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1020,7 +1020,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1113,7 +1113,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1146,7 +1146,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -3732,7 +3732,7 @@
     <row r="12" ht="45" customHeight="1" s="42">
       <c r="A12" s="63" t="inlineStr">
         <is>
-          <t>Sprint 2 ✅</t>
+          <t>Sprint 2 ⚠ (audit 01/07)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E12" s="63" t="inlineStr">
         <is>
-          <t>14 (réel)</t>
+          <t>3 réel / 14 engagé</t>
         </is>
       </c>
       <c r="F12" s="63" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="H12" s="63" t="inlineStr">
         <is>
-          <t>⚡ J3 Sécurité LLM &amp; RGPD (mercredi 09h) · 🚀 Release 1 (MVP) livré 17h45</t>
+          <t>⚡ J3 Sécurité LLM &amp; RGPD (mercredi 09h) · 🚀 Release 1 (MVP) démo 17h45 — audit code du 01/07 : seul US-SEC-02 (3 SP) réellement Done, US-SEC-01/US-RGPD-02 en cours, US-RGPD-01/US-SEC-03 pas faits (voir Sprint Backlog v2.1)</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="76" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E11" s="75" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="I11" s="77" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="24.75" customHeight="1" s="42">
